--- a/data/import_ready/students.xlsx
+++ b/data/import_ready/students.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Имя</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>telegram</t>
+          <t>Телеграм</t>
         </is>
       </c>
     </row>

--- a/data/import_ready/students.xlsx
+++ b/data/import_ready/students.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>ФИО</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
